--- a/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>14.91234014872242</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>13.52702466544904</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>13.90443619255264</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>13.71846870037534</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>12.8919280498089</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>13.13965873064551</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         <v>14.98568732088275</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -606,7 +606,7 @@
         <v>12.89427310845661</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +633,7 @@
         <v>13.63681631997073</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v>14.44186917204651</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>12.98033777942806</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -714,7 +714,7 @@
         <v>13.38468956102126</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -741,7 +741,7 @@
         <v>13.34608331119034</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -768,7 +768,7 @@
         <v>12.32375491160378</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -795,13 +795,13 @@
         <v>12.65035627986977</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="C17">
-        <v>1040462.12</v>
+        <v>981496.9399999999</v>
       </c>
       <c r="D17">
-        <v>919745.0600000001</v>
+        <v>863577.88</v>
       </c>
       <c r="E17">
-        <v>120717.0599999999</v>
+        <v>117919.0599999999</v>
       </c>
       <c r="F17">
-        <v>13.1250566325412</v>
+        <v>13.65471056298939</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,25 +837,25 @@
         </is>
       </c>
       <c r="C18">
-        <v>1247474.62</v>
+        <v>1214101.88</v>
       </c>
       <c r="D18">
-        <v>1107881.12</v>
+        <v>1076903.38</v>
       </c>
       <c r="E18">
-        <v>139593.5</v>
+        <v>137198.5</v>
       </c>
       <c r="F18">
-        <v>12.60004322485431</v>
+        <v>12.74009373060006</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="C19">
-        <v>1155245</v>
+        <v>1113305.25</v>
       </c>
       <c r="D19">
-        <v>1024937.75</v>
+        <v>985180.3100000001</v>
       </c>
       <c r="E19">
-        <v>130307.25</v>
+        <v>128124.9399999999</v>
       </c>
       <c r="F19">
-        <v>12.71367456218682</v>
+        <v>13.00522743902586</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="C20">
-        <v>1166270.38</v>
+        <v>1040462.12</v>
       </c>
       <c r="D20">
-        <v>1025931.12</v>
+        <v>919745.0600000001</v>
       </c>
       <c r="E20">
-        <v>140339.2599999999</v>
+        <v>120717.0599999999</v>
       </c>
       <c r="F20">
-        <v>13.67920879522593</v>
+        <v>13.1250566325412</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -918,25 +918,25 @@
         </is>
       </c>
       <c r="C21">
-        <v>1217801</v>
+        <v>1247474.62</v>
       </c>
       <c r="D21">
-        <v>1116255.12</v>
+        <v>1107881.12</v>
       </c>
       <c r="E21">
-        <v>101545.8799999999</v>
+        <v>139593.5</v>
       </c>
       <c r="F21">
-        <v>9.097013593093294</v>
+        <v>12.60004322485431</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="C22">
-        <v>1191589.88</v>
+        <v>1155245</v>
       </c>
       <c r="D22">
-        <v>1069051.75</v>
+        <v>1024937.75</v>
       </c>
       <c r="E22">
-        <v>122538.1299999999</v>
+        <v>130307.25</v>
       </c>
       <c r="F22">
-        <v>11.46231976141472</v>
+        <v>12.71367456218682</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="C23">
-        <v>974676.38</v>
+        <v>1166270.38</v>
       </c>
       <c r="D23">
-        <v>850477.75</v>
+        <v>1025931.12</v>
       </c>
       <c r="E23">
-        <v>124198.63</v>
+        <v>140339.2599999999</v>
       </c>
       <c r="F23">
-        <v>14.60339556208261</v>
+        <v>13.67920879522593</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -999,45 +999,126 @@
         </is>
       </c>
       <c r="C24">
-        <v>1383428</v>
+        <v>1217801</v>
       </c>
       <c r="D24">
-        <v>1218459.62</v>
+        <v>1116255.12</v>
       </c>
       <c r="E24">
-        <v>164968.3799999999</v>
+        <v>101545.8799999999</v>
       </c>
       <c r="F24">
-        <v>13.53909290814248</v>
+        <v>9.097013593093294</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>1191589.88</v>
+      </c>
+      <c r="D25">
+        <v>1069051.75</v>
+      </c>
+      <c r="E25">
+        <v>122538.1299999999</v>
+      </c>
+      <c r="F25">
+        <v>11.46231976141472</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Los Andes</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>974676.38</v>
+      </c>
+      <c r="D26">
+        <v>850477.75</v>
+      </c>
+      <c r="E26">
+        <v>124198.63</v>
+      </c>
+      <c r="F26">
+        <v>14.60339556208261</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1383428</v>
+      </c>
+      <c r="D27">
+        <v>1218459.62</v>
+      </c>
+      <c r="E27">
+        <v>164968.3799999999</v>
+      </c>
+      <c r="F27">
+        <v>13.53909290814248</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C28">
         <v>1218693.5</v>
       </c>
-      <c r="D25">
+      <c r="D28">
         <v>1070166.12</v>
       </c>
-      <c r="E25">
+      <c r="E28">
         <v>148527.3799999999</v>
       </c>
-      <c r="F25">
+      <c r="F28">
         <v>13.87890881838045</v>
       </c>
-      <c r="G25">
+      <c r="G28">
         <v>1</v>
       </c>
     </row>
@@ -1140,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1597,6 +1678,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>985180.3100000001</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1113305.25</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>1190907.5</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:06</t>
+    <t xml:space="preserve">2026-08-19 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -98,13 +98,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_a_2023_valparaiso.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de asalariados formales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -1193,23 +1199,23 @@
         <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1313,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
@@ -1324,7 +1330,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1069051.75</v>
@@ -1335,7 +1341,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1191589.88</v>
@@ -1346,7 +1352,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1262107.5</v>
@@ -1357,7 +1363,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1070166.12</v>
@@ -1368,7 +1374,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>1218693.5</v>
@@ -1379,7 +1385,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>1295152.12</v>
@@ -1390,7 +1396,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>987235.12</v>
@@ -1401,7 +1407,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1112123.88</v>
@@ -1412,7 +1418,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1189921.5</v>
@@ -1423,7 +1429,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>878812.62</v>
@@ -1434,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>1001006.56</v>
@@ -1445,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1071068.75</v>
@@ -1456,7 +1462,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>962238.38</v>
@@ -1467,7 +1473,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>1091031</v>
@@ -1478,7 +1484,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>1173103.88</v>
@@ -1489,7 +1495,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>903701.62</v>
@@ -1500,7 +1506,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>1026937.75</v>
@@ -1511,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>1098884.12</v>
@@ -1522,7 +1528,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>885639.44</v>
@@ -1533,7 +1539,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>1002009.44</v>
@@ -1544,7 +1550,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>1079717.38</v>
@@ -1555,7 +1561,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>1024937.75</v>
@@ -1566,7 +1572,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>1155245</v>
@@ -1577,7 +1583,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>1233714.5</v>
@@ -1588,7 +1594,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>985180.31</v>
@@ -1599,7 +1605,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>1113305.25</v>
@@ -1610,7 +1616,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>1190907.5</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:24</t>
+    <t xml:space="preserve">2026-09-07 11:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
